--- a/20241128110837-csh.xlsx
+++ b/20241128110837-csh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12360"/>
+    <workbookView windowWidth="27320" windowHeight="10060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,12 +12,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$62</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="423">
   <si>
     <t>用户名</t>
   </si>
@@ -212,6 +225,9 @@
   </si>
   <si>
     <t>testXFDF.xfdf</t>
+  </si>
+  <si>
+    <t>办公文档111111111111</t>
   </si>
   <si>
     <t>PDF文档</t>
@@ -2585,13 +2601,13 @@
         <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>30</v>
@@ -2630,10 +2646,10 @@
         <v>53</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="U5" s="2" t="s">
         <v>44</v>
@@ -2645,7 +2661,7 @@
         <v>45</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" ht="17.6" spans="1:24">
@@ -2656,16 +2672,16 @@
         <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>30</v>
@@ -2704,10 +2720,10 @@
         <v>53</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U6" s="2" t="s">
         <v>44</v>
@@ -2719,7 +2735,7 @@
         <v>45</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" ht="17.6" hidden="1" spans="1:24">
@@ -2730,16 +2746,16 @@
         <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>30</v>
@@ -2775,13 +2791,13 @@
         <v>40</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>44</v>
@@ -2793,7 +2809,7 @@
         <v>45</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" ht="17.6" spans="1:24">
@@ -2804,16 +2820,16 @@
         <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>30</v>
@@ -2849,13 +2865,13 @@
         <v>52</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>44</v>
@@ -2867,7 +2883,7 @@
         <v>45</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" ht="17.6" spans="1:24">
@@ -2878,16 +2894,16 @@
         <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>30</v>
@@ -2923,13 +2939,13 @@
         <v>52</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>44</v>
@@ -2941,7 +2957,7 @@
         <v>45</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" ht="17.6" hidden="1" spans="1:24">
@@ -2952,16 +2968,16 @@
         <v>25</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>30</v>
@@ -2997,13 +3013,13 @@
         <v>40</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>44</v>
@@ -3015,7 +3031,7 @@
         <v>45</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" ht="17.6" spans="1:24">
@@ -3026,16 +3042,16 @@
         <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>30</v>
@@ -3071,13 +3087,13 @@
         <v>52</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>44</v>
@@ -3089,7 +3105,7 @@
         <v>45</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" ht="17.6" spans="1:24">
@@ -3100,16 +3116,16 @@
         <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>30</v>
@@ -3145,13 +3161,13 @@
         <v>52</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U12" s="2" t="s">
         <v>44</v>
@@ -3163,7 +3179,7 @@
         <v>45</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" ht="17.6" spans="1:24">
@@ -3174,16 +3190,16 @@
         <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>30</v>
@@ -3219,13 +3235,13 @@
         <v>52</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U13" s="2" t="s">
         <v>44</v>
@@ -3237,7 +3253,7 @@
         <v>45</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" ht="17.6" spans="1:24">
@@ -3248,16 +3264,16 @@
         <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>30</v>
@@ -3293,13 +3309,13 @@
         <v>52</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="U14" s="2" t="s">
         <v>44</v>
@@ -3311,7 +3327,7 @@
         <v>45</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" ht="17.6" spans="1:24">
@@ -3322,16 +3338,16 @@
         <v>25</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>30</v>
@@ -3367,13 +3383,13 @@
         <v>52</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U15" s="2" t="s">
         <v>44</v>
@@ -3385,7 +3401,7 @@
         <v>45</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" ht="17.6" spans="1:24">
@@ -3396,16 +3412,16 @@
         <v>25</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>30</v>
@@ -3441,13 +3457,13 @@
         <v>52</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U16" s="2" t="s">
         <v>44</v>
@@ -3459,7 +3475,7 @@
         <v>45</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" ht="17.6" spans="1:24">
@@ -3470,16 +3486,16 @@
         <v>25</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>30</v>
@@ -3518,10 +3534,10 @@
         <v>53</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="U17" s="2" t="s">
         <v>44</v>
@@ -3533,7 +3549,7 @@
         <v>45</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" ht="17.6" spans="1:24">
@@ -3544,16 +3560,16 @@
         <v>25</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>30</v>
@@ -3592,10 +3608,10 @@
         <v>53</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="U18" s="2" t="s">
         <v>44</v>
@@ -3607,7 +3623,7 @@
         <v>45</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" ht="17.6" hidden="1" spans="1:24">
@@ -3618,16 +3634,16 @@
         <v>25</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>30</v>
@@ -3663,13 +3679,13 @@
         <v>40</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="U19" s="2" t="s">
         <v>44</v>
@@ -3681,7 +3697,7 @@
         <v>45</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" ht="17.6" spans="1:24">
@@ -3692,16 +3708,16 @@
         <v>25</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>30</v>
@@ -3740,10 +3756,10 @@
         <v>53</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="U20" s="2" t="s">
         <v>44</v>
@@ -3755,7 +3771,7 @@
         <v>45</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" ht="17.6" spans="1:24">
@@ -3766,16 +3782,16 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>30</v>
@@ -3814,10 +3830,10 @@
         <v>53</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U21" s="2" t="s">
         <v>44</v>
@@ -3829,7 +3845,7 @@
         <v>45</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" ht="17.6" spans="1:24">
@@ -3840,16 +3856,16 @@
         <v>25</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>30</v>
@@ -3888,10 +3904,10 @@
         <v>53</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U22" s="2" t="s">
         <v>44</v>
@@ -3903,7 +3919,7 @@
         <v>45</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" ht="17.6" spans="1:24">
@@ -3914,16 +3930,16 @@
         <v>25</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>30</v>
@@ -3962,10 +3978,10 @@
         <v>53</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="U23" s="2" t="s">
         <v>44</v>
@@ -3977,7 +3993,7 @@
         <v>45</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" ht="17.6" spans="1:24">
@@ -3988,16 +4004,16 @@
         <v>25</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>30</v>
@@ -4033,13 +4049,13 @@
         <v>52</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="U24" s="2" t="s">
         <v>44</v>
@@ -4051,7 +4067,7 @@
         <v>45</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" ht="17.6" spans="1:24">
@@ -4062,16 +4078,16 @@
         <v>25</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>30</v>
@@ -4110,10 +4126,10 @@
         <v>53</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="U25" s="2" t="s">
         <v>44</v>
@@ -4125,7 +4141,7 @@
         <v>45</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" ht="17.6" spans="1:24">
@@ -4136,16 +4152,16 @@
         <v>25</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>30</v>
@@ -4184,10 +4200,10 @@
         <v>53</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="U26" s="2" t="s">
         <v>44</v>
@@ -4199,7 +4215,7 @@
         <v>45</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" ht="17.6" spans="1:24">
@@ -4210,16 +4226,16 @@
         <v>25</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>30</v>
@@ -4258,10 +4274,10 @@
         <v>53</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="U27" s="2" t="s">
         <v>44</v>
@@ -4273,7 +4289,7 @@
         <v>45</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" ht="17.6" spans="1:24">
@@ -4284,16 +4300,16 @@
         <v>25</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>30</v>
@@ -4332,10 +4348,10 @@
         <v>53</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U28" s="2" t="s">
         <v>44</v>
@@ -4347,7 +4363,7 @@
         <v>45</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" ht="17.6" spans="1:24">
@@ -4358,16 +4374,16 @@
         <v>25</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>30</v>
@@ -4406,10 +4422,10 @@
         <v>53</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U29" s="2" t="s">
         <v>44</v>
@@ -4421,7 +4437,7 @@
         <v>45</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" ht="17.6" hidden="1" spans="1:24">
@@ -4432,16 +4448,16 @@
         <v>25</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>30</v>
@@ -4477,13 +4493,13 @@
         <v>40</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="U30" s="2" t="s">
         <v>44</v>
@@ -4495,7 +4511,7 @@
         <v>45</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" ht="17.6" spans="1:24">
@@ -4506,16 +4522,16 @@
         <v>25</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>30</v>
@@ -4551,13 +4567,13 @@
         <v>52</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="U31" s="2" t="s">
         <v>44</v>
@@ -4569,7 +4585,7 @@
         <v>45</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" ht="17.6" spans="1:24">
@@ -4580,16 +4596,16 @@
         <v>25</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>30</v>
@@ -4625,13 +4641,13 @@
         <v>52</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="U32" s="2" t="s">
         <v>44</v>
@@ -4643,7 +4659,7 @@
         <v>45</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" ht="17.6" hidden="1" spans="1:24">
@@ -4654,16 +4670,16 @@
         <v>25</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>30</v>
@@ -4699,13 +4715,13 @@
         <v>40</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>44</v>
@@ -4717,7 +4733,7 @@
         <v>45</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" ht="17.6" spans="1:24">
@@ -4728,16 +4744,16 @@
         <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>30</v>
@@ -4773,13 +4789,13 @@
         <v>52</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="U34" s="2" t="s">
         <v>44</v>
@@ -4791,7 +4807,7 @@
         <v>45</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" ht="17.6" spans="1:24">
@@ -4802,16 +4818,16 @@
         <v>25</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>30</v>
@@ -4850,10 +4866,10 @@
         <v>53</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>44</v>
@@ -4865,7 +4881,7 @@
         <v>45</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="36" ht="17.6" hidden="1" spans="1:24">
@@ -4876,16 +4892,16 @@
         <v>25</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>30</v>
@@ -4921,13 +4937,13 @@
         <v>40</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="U36" s="2" t="s">
         <v>44</v>
@@ -4939,7 +4955,7 @@
         <v>45</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37" ht="17.6" hidden="1" spans="1:24">
@@ -4950,16 +4966,16 @@
         <v>25</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>30</v>
@@ -4995,13 +5011,13 @@
         <v>40</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>44</v>
@@ -5013,7 +5029,7 @@
         <v>45</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38" ht="17.6" hidden="1" spans="1:24">
@@ -5024,16 +5040,16 @@
         <v>25</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>30</v>
@@ -5069,13 +5085,13 @@
         <v>40</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>44</v>
@@ -5087,7 +5103,7 @@
         <v>45</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39" ht="17.6" hidden="1" spans="1:24">
@@ -5098,16 +5114,16 @@
         <v>25</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>30</v>
@@ -5143,13 +5159,13 @@
         <v>40</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="U39" s="2" t="s">
         <v>44</v>
@@ -5161,7 +5177,7 @@
         <v>45</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40" ht="17.6" spans="1:24">
@@ -5172,16 +5188,16 @@
         <v>25</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>30</v>
@@ -5220,10 +5236,10 @@
         <v>53</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>44</v>
@@ -5235,7 +5251,7 @@
         <v>45</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" ht="17.6" hidden="1" spans="1:24">
@@ -5246,16 +5262,16 @@
         <v>25</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>30</v>
@@ -5291,13 +5307,13 @@
         <v>40</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U41" s="2" t="s">
         <v>44</v>
@@ -5309,7 +5325,7 @@
         <v>45</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" ht="17.6" hidden="1" spans="1:24">
@@ -5320,16 +5336,16 @@
         <v>25</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>30</v>
@@ -5365,13 +5381,13 @@
         <v>40</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="U42" s="2" t="s">
         <v>44</v>
@@ -5383,7 +5399,7 @@
         <v>45</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" ht="17.6" spans="1:24">
@@ -5394,16 +5410,16 @@
         <v>25</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>30</v>
@@ -5439,13 +5455,13 @@
         <v>52</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>44</v>
@@ -5457,7 +5473,7 @@
         <v>45</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="44" ht="17.6" hidden="1" spans="1:24">
@@ -5468,16 +5484,16 @@
         <v>25</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>30</v>
@@ -5513,13 +5529,13 @@
         <v>40</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="U44" s="2" t="s">
         <v>44</v>
@@ -5531,7 +5547,7 @@
         <v>45</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45" ht="17.6" hidden="1" spans="1:24">
@@ -5542,16 +5558,16 @@
         <v>25</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>30</v>
@@ -5587,13 +5603,13 @@
         <v>40</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="U45" s="2" t="s">
         <v>44</v>
@@ -5605,7 +5621,7 @@
         <v>45</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="46" ht="17.6" hidden="1" spans="1:24">
@@ -5616,16 +5632,16 @@
         <v>25</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>30</v>
@@ -5661,13 +5677,13 @@
         <v>40</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="U46" s="2" t="s">
         <v>44</v>
@@ -5679,7 +5695,7 @@
         <v>45</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" ht="17.6" hidden="1" spans="1:24">
@@ -5690,16 +5706,16 @@
         <v>25</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>30</v>
@@ -5735,13 +5751,13 @@
         <v>40</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="U47" s="2" t="s">
         <v>44</v>
@@ -5753,7 +5769,7 @@
         <v>45</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" ht="17.6" hidden="1" spans="1:24">
@@ -5764,16 +5780,16 @@
         <v>25</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>30</v>
@@ -5809,13 +5825,13 @@
         <v>40</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="U48" s="2" t="s">
         <v>44</v>
@@ -5827,7 +5843,7 @@
         <v>45</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="49" ht="17.6" spans="1:24">
@@ -5838,16 +5854,16 @@
         <v>25</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>30</v>
@@ -5886,10 +5902,10 @@
         <v>53</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="U49" s="2" t="s">
         <v>44</v>
@@ -5901,7 +5917,7 @@
         <v>45</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="50" ht="17.6" spans="1:24">
@@ -5912,16 +5928,16 @@
         <v>25</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>30</v>
@@ -5960,10 +5976,10 @@
         <v>53</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="U50" s="2" t="s">
         <v>44</v>
@@ -5975,7 +5991,7 @@
         <v>45</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="51" ht="17.6" hidden="1" spans="1:24">
@@ -5986,16 +6002,16 @@
         <v>25</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>30</v>
@@ -6025,19 +6041,19 @@
         <v>38</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q51" s="2" t="s">
         <v>40</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="U51" s="2" t="s">
         <v>44</v>
@@ -6049,7 +6065,7 @@
         <v>45</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="52" ht="17.6" hidden="1" spans="1:24">
@@ -6060,16 +6076,16 @@
         <v>25</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>30</v>
@@ -6105,13 +6121,13 @@
         <v>40</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U52" s="2" t="s">
         <v>44</v>
@@ -6123,7 +6139,7 @@
         <v>45</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="53" ht="17.6" hidden="1" spans="1:24">
@@ -6134,16 +6150,16 @@
         <v>25</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>30</v>
@@ -6173,19 +6189,19 @@
         <v>38</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="U53" s="2" t="s">
         <v>44</v>
@@ -6197,7 +6213,7 @@
         <v>45</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="54" ht="17.6" hidden="1" spans="1:24">
@@ -6208,16 +6224,16 @@
         <v>25</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>30</v>
@@ -6253,13 +6269,13 @@
         <v>40</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="U54" s="2" t="s">
         <v>44</v>
@@ -6271,7 +6287,7 @@
         <v>45</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="55" ht="17.6" spans="1:24">
@@ -6282,16 +6298,16 @@
         <v>25</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>30</v>
@@ -6324,16 +6340,16 @@
         <v>51</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="U55" s="2" t="s">
         <v>44</v>
@@ -6345,7 +6361,7 @@
         <v>45</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="56" ht="17.6" spans="1:24">
@@ -6356,16 +6372,16 @@
         <v>25</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>30</v>
@@ -6398,16 +6414,16 @@
         <v>51</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="U56" s="2" t="s">
         <v>44</v>
@@ -6419,7 +6435,7 @@
         <v>45</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="57" ht="17.6" spans="1:24">
@@ -6430,16 +6446,16 @@
         <v>25</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>30</v>
@@ -6472,16 +6488,16 @@
         <v>51</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="U57" s="2" t="s">
         <v>44</v>
@@ -6493,7 +6509,7 @@
         <v>45</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="58" ht="17.6" hidden="1" spans="1:24">
@@ -6504,16 +6520,16 @@
         <v>25</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>30</v>
@@ -6525,7 +6541,7 @@
         <v>32</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>34</v>
@@ -6543,19 +6559,19 @@
         <v>38</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U58" s="2" t="s">
         <v>44</v>
@@ -6567,7 +6583,7 @@
         <v>45</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="59" ht="17.6" hidden="1" spans="1:24">
@@ -6578,16 +6594,16 @@
         <v>25</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>30</v>
@@ -6617,19 +6633,19 @@
         <v>38</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="U59" s="2" t="s">
         <v>44</v>
@@ -6641,7 +6657,7 @@
         <v>45</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="60" ht="17.6" hidden="1" spans="1:24">
@@ -6652,16 +6668,16 @@
         <v>25</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>30</v>
@@ -6673,7 +6689,7 @@
         <v>32</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>34</v>
@@ -6691,19 +6707,19 @@
         <v>38</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="U60" s="2" t="s">
         <v>44</v>
@@ -6715,7 +6731,7 @@
         <v>45</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="61" ht="17.6" hidden="1" spans="1:24">
@@ -6726,16 +6742,16 @@
         <v>25</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>30</v>
@@ -6765,19 +6781,19 @@
         <v>38</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U61" s="2" t="s">
         <v>44</v>
@@ -6789,7 +6805,7 @@
         <v>45</v>
       </c>
       <c r="X61" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="62" ht="17.6" hidden="1" spans="1:24">
@@ -6800,16 +6816,16 @@
         <v>25</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>30</v>
@@ -6821,7 +6837,7 @@
         <v>32</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>34</v>
@@ -6839,19 +6855,19 @@
         <v>38</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="U62" s="2" t="s">
         <v>44</v>
@@ -6863,15 +6879,15 @@
         <v>45</v>
       </c>
       <c r="X62" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X62">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:X62" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="15">
-      <filters>
-        <filter val="[csh-综合1017]"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="[csh-综合1017]"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>

--- a/20241128110837-csh.xlsx
+++ b/20241128110837-csh.xlsx
@@ -227,7 +227,7 @@
     <t>testXFDF.xfdf</t>
   </si>
   <si>
-    <t>办公文档111111111111</t>
+    <t>办公文档11eeee1111111111</t>
   </si>
   <si>
     <t>PDF文档</t>

--- a/20241128110837-csh.xlsx
+++ b/20241128110837-csh.xlsx
@@ -227,7 +227,7 @@
     <t>testXFDF.xfdf</t>
   </si>
   <si>
-    <t>办公文档11eeee1111111111</t>
+    <t>办公文档11eeee11sss11111111</t>
   </si>
   <si>
     <t>PDF文档</t>

--- a/20241128110837-csh.xlsx
+++ b/20241128110837-csh.xlsx
@@ -224,10 +224,10 @@
     <t>/Users/chengshanhong/Documents/test_files/testsolidworksAssembly2013SP2.SLDASM</t>
   </si>
   <si>
-    <t>testXFDF.xfdf</t>
-  </si>
-  <si>
-    <t>办公文档11eeee11sss11111111</t>
+    <t>testXFDF.xfdfcdscdscds</t>
+  </si>
+  <si>
+    <t>办公文档11eeee3311sss11111111</t>
   </si>
   <si>
     <t>PDF文档</t>

--- a/20241128110837-csh.xlsx
+++ b/20241128110837-csh.xlsx
@@ -338,7 +338,7 @@
     <t>/Users/chengshanhong/Documents/test_files/testWORD.docx</t>
   </si>
   <si>
-    <t>testVISIO.vstx</t>
+    <t>cvf</t>
   </si>
   <si>
     <t>Visio文档</t>

--- a/20241128110837-csh.xlsx
+++ b/20241128110837-csh.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27320" windowHeight="10060"/>
+    <workbookView windowWidth="21420" windowHeight="7440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -338,7 +338,7 @@
     <t>/Users/chengshanhong/Documents/test_files/testWORD.docx</t>
   </si>
   <si>
-    <t>cvf</t>
+    <t>cvfv 肉如果</t>
   </si>
   <si>
     <t>Visio文档</t>
